--- a/Data/SPY_companies_info.xlsx
+++ b/Data/SPY_companies_info.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3,745.25B</t>
+          <t>3,748.12B</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3,307.86B</t>
+          <t>3,363.46B</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3,296.11B</t>
+          <t>3,342.43B</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2,366.30B</t>
+          <t>2,407.62B</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2,274.19B</t>
+          <t>2,359.02B</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2,266.67B</t>
+          <t>2,349.78B</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1,563.47B</t>
+          <t>1,592.42B</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1,287.20B</t>
+          <t>1,342.13B</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>997.81B</t>
+          <t>988.39B</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>802.45B</t>
+          <t>843.79B</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>759.56B</t>
+          <t>755.86B</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>719.97B</t>
+          <t>704.45B</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>683.73B</t>
+          <t>679.99B</t>
         </is>
       </c>
     </row>
@@ -679,75 +679,75 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>612.18B</t>
+          <t>615.81B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UnitedHealth Group Incorporated</t>
+          <t>Exxon Mobil Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>520.14B</t>
+          <t>491.46B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>495.20B</t>
+          <t>490.36B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>492.53B</t>
+          <t>488.66B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>UnitedHealth Group Incorporated</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>485.54B</t>
+          <t>474.65B</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>440.15B</t>
+          <t>437.93B</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>419.79B</t>
+          <t>411.67B</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>405.73B</t>
+          <t>402.36B</t>
         </is>
       </c>
     </row>
@@ -815,41 +815,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>390.42B</t>
+          <t>395.63B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>359.29B</t>
+          <t>353.57B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>351.03B</t>
+          <t>352.09B</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>333.82B</t>
+          <t>342.63B</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>310.43B</t>
+          <t>306.05B</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>282.14B</t>
+          <t>278.03B</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>271.00B</t>
+          <t>275.01B</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>270.97B</t>
+          <t>270.71B</t>
         </is>
       </c>
     </row>
@@ -951,24 +951,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>255.49B</t>
+          <t>256.13B</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adobe Inc.</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>240.81B</t>
+          <t>236.94B</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>239.89B</t>
+          <t>235.73B</t>
         </is>
       </c>
     </row>
@@ -1002,75 +1002,75 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>233.87B</t>
+          <t>234.39B</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>232.69B</t>
+          <t>232.47B</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>231.58B</t>
+          <t>225.06B</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>226.76B</t>
+          <t>220.54B</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PepsiCo, Inc.</t>
+          <t>International Business Machines Corporation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>221.85B</t>
+          <t>214.76B</t>
         </is>
       </c>
     </row>
@@ -1087,24 +1087,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>215.49B</t>
+          <t>212.57B</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>214.26B</t>
+          <t>211.94B</t>
         </is>
       </c>
     </row>
@@ -1121,126 +1121,126 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>212.82B</t>
+          <t>211.54B</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Adobe Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>211.80B</t>
+          <t>208.93B</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>207.77B</t>
+          <t>208.80B</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>207.30B</t>
+          <t>208.08B</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc.</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>204.96B</t>
+          <t>206.07B</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Thermo Fisher Scientific Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>204.26B</t>
+          <t>200.81B</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc.</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>200.54B</t>
+          <t>197.49B</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Philip Morris International Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>200.33B</t>
+          <t>197.46B</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>192.60B</t>
+          <t>194.77B</t>
         </is>
       </c>
     </row>
@@ -1274,58 +1274,58 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>191.66B</t>
+          <t>194.02B</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>187.52B</t>
+          <t>188.25B</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General Electric Company</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>185.36B</t>
+          <t>183.84B</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intuit Inc.</t>
+          <t>General Electric Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>181.20B</t>
+          <t>178.39B</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>178.07B</t>
+          <t>177.14B</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>173.83B</t>
+          <t>175.80B</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>173.49B</t>
+          <t>174.88B</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>171.62B</t>
+          <t>174.38B</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>169.26B</t>
+          <t>169.37B</t>
         </is>
       </c>
     </row>
@@ -1427,41 +1427,41 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>168.69B</t>
+          <t>167.61B</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BlackRock, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>163.72B</t>
+          <t>166.75B</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>BlackRock, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>161.49B</t>
+          <t>163.99B</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>158.75B</t>
+          <t>158.97B</t>
         </is>
       </c>
     </row>
@@ -1495,75 +1495,75 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>156.54B</t>
+          <t>154.46B</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lowe's Companies, Inc.</t>
+          <t>Comcast Corporation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>152.52B</t>
+          <t>153.98B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NextEra Energy, Inc.</t>
+          <t>The Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>152.46B</t>
+          <t>151.66B</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Comcast Corporation</t>
+          <t>NextEra Energy, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>151.26B</t>
+          <t>150.57B</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation</t>
+          <t>Lowe's Companies, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>150.69B</t>
+          <t>148.79B</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>148.96B</t>
+          <t>148.05B</t>
         </is>
       </c>
     </row>
@@ -1597,41 +1597,41 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>148.22B</t>
+          <t>147.32B</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>145.88B</t>
+          <t>143.77B</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>144.90B</t>
+          <t>142.98B</t>
         </is>
       </c>
     </row>
@@ -1648,58 +1648,58 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>144.85B</t>
+          <t>142.21B</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>The TJX Companies, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>143.74B</t>
+          <t>142.12B</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The TJX Companies, Inc.</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>142.99B</t>
+          <t>141.73B</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>141.68B</t>
+          <t>141.69B</t>
         </is>
       </c>
     </row>
@@ -1716,58 +1716,58 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>138.64B</t>
+          <t>139.39B</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Citigroup Inc.</t>
+          <t>KKR &amp; Co. Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>137.12B</t>
+          <t>138.34B</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>Citigroup Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>136.79B</t>
+          <t>135.09B</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc.</t>
+          <t>Arista Networks Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>134.84B</t>
+          <t>134.64B</t>
         </is>
       </c>
     </row>
@@ -1784,262 +1784,262 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>132.94B</t>
+          <t>133.26B</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>132.41B</t>
+          <t>131.31B</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arista Networks Inc</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>132.00B</t>
+          <t>130.53B</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>127.88B</t>
+          <t>129.31B</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>The Boeing Company</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>123.15B</t>
+          <t>125.34B</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Boeing Company</t>
+          <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>122.61B</t>
+          <t>121.73B</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corporation</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>121.58B</t>
+          <t>120.24B</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Vertex Pharmaceuticals Incorporated</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>121.47B</t>
+          <t>119.52B</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals Incorporated</t>
+          <t>Lockheed Martin Corporation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>120.84B</t>
+          <t>117.71B</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Company</t>
+          <t>Fiserv, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>117.88B</t>
+          <t>116.54B</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gilead Sciences, Inc.</t>
+          <t>NIKE, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>115.08B</t>
+          <t>116.04B</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fiserv, Inc.</t>
+          <t>Gilead Sciences, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>114.66B</t>
+          <t>115.13B</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NIKE, Inc.</t>
+          <t>Bristol-Myers Squibb Company</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>114.23B</t>
+          <t>114.15B</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Starbucks Corporation</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>111.29B</t>
+          <t>111.01B</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>United Parcel Service, Inc.</t>
+          <t>Starbucks Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>111.13B</t>
+          <t>110.91B</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>United Parcel Service, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>110.69B</t>
+          <t>110.07B</t>
         </is>
       </c>
     </row>
@@ -2056,75 +2056,75 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>108.77B</t>
+          <t>108.92B</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Medtronic plc</t>
+          <t>Analog Devices, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>107.17B</t>
+          <t>108.05B</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Analog Devices, Inc.</t>
+          <t>Medtronic plc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>107.01B</t>
+          <t>106.08B</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Prologis, Inc.</t>
+          <t>Marsh &amp; McLennan Companies, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>106.58B</t>
+          <t>106.04B</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Marsh &amp; McLennan Companies, Inc.</t>
+          <t>Prologis, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>105.88B</t>
+          <t>105.17B</t>
         </is>
       </c>
     </row>
@@ -2141,41 +2141,41 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>96.67B</t>
+          <t>97.25B</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Altria Group, Inc.</t>
+          <t>Equinix, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>94.05B</t>
+          <t>94.10B</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Sherwin-Williams Company</t>
+          <t>Altria Group, Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>93.27B</t>
+          <t>93.20B</t>
         </is>
       </c>
     </row>
@@ -2192,24 +2192,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>93.24B</t>
+          <t>92.45B</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equinix, Inc.</t>
+          <t>The Sherwin-Williams Company</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>92.79B</t>
+          <t>92.08B</t>
         </is>
       </c>
     </row>
@@ -2226,58 +2226,58 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>92.46B</t>
+          <t>91.35B</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange, Inc.</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>90.96B</t>
+          <t>90.94B</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Elevance Health, Inc.</t>
+          <t>Chipotle Mexican Grill, Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>90.42B</t>
+          <t>90.22B</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>90.25B</t>
+          <t>90.03B</t>
         </is>
       </c>
     </row>
@@ -2294,347 +2294,347 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>89.43B</t>
+          <t>89.93B</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Moody's Corporation</t>
+          <t>Intercontinental Exchange, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>89.07B</t>
+          <t>89.89B</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PayPal Holdings, Inc.</t>
+          <t>Moody's Corporation</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>88.99B</t>
+          <t>89.66B</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill, Inc.</t>
+          <t>PayPal Holdings, Inc.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>88.40B</t>
+          <t>89.63B</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Amphenol Corporation</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>87.54B</t>
+          <t>89.62B</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Parker-Hannifin Corporation</t>
+          <t>Amphenol Corporation</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>87.26B</t>
+          <t>88.73B</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Parker-Hannifin Corporation</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>86.95B</t>
+          <t>87.86B</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Waste Management, Inc.</t>
+          <t>Elevance Health, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>86.73B</t>
+          <t>87.76B</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>86.61B</t>
+          <t>86.49B</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Airbnb, Inc.</t>
+          <t>Waste Management, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>86.41B</t>
+          <t>86.07B</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CME Group Inc.</t>
+          <t>Airbnb, Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>86.20B</t>
+          <t>85.89B</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Cintas Corporation</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>85.86B</t>
+          <t>85.33B</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Duke Energy Corporation</t>
+          <t>CME Group Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>85.83B</t>
+          <t>85.03B</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Cadence Design Systems, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>85.41B</t>
+          <t>84.53B</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cintas Corporation</t>
+          <t>Duke Energy Corporation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>84.75B</t>
+          <t>84.32B</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals, Inc.</t>
+          <t>Mondelez International, Inc.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>83.76B</t>
+          <t>83.75B</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cadence Design Systems, Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>83.06B</t>
+          <t>83.48B</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mondelez International, Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>82.57B</t>
+          <t>80.69B</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Illinois Tool Works Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>81.83B</t>
+          <t>80.65B</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>The PNC Financial Services Group, Inc.</t>
+          <t>Marriott International, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>81.12B</t>
+          <t>80.59B</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Illinois Tool Works Inc.</t>
+          <t>The PNC Financial Services Group, Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>80.84B</t>
+          <t>80.27B</t>
         </is>
       </c>
     </row>
@@ -2651,126 +2651,126 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>80.50B</t>
+          <t>79.98B</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Regeneron Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>80.45B</t>
+          <t>79.72B</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HCA Healthcare, Inc.</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>80.24B</t>
+          <t>79.72B</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Marriott International, Inc.</t>
+          <t>HCA Healthcare, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>79.94B</t>
+          <t>79.03B</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>79.73B</t>
+          <t>78.71B</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Motorola Solutions, Inc.</t>
+          <t>Synopsys, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>79.72B</t>
+          <t>78.61B</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Aon plc</t>
+          <t>Motorola Solutions, Inc.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>78.13B</t>
+          <t>78.53B</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Synopsys, Inc.</t>
+          <t>Aon plc</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>77.62B</t>
+          <t>78.44B</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>76.71B</t>
+          <t>76.44B</t>
         </is>
       </c>
     </row>
@@ -2804,58 +2804,58 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>74.45B</t>
+          <t>75.57B</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Dynamics Corporation</t>
+          <t>Emerson Electric Co.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>74.24B</t>
+          <t>75.12B</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Constellation Energy Corporation</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>74.13B</t>
+          <t>74.76B</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Emerson Electric Co.</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>73.96B</t>
+          <t>73.54B</t>
         </is>
       </c>
     </row>
@@ -2872,24 +2872,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>73.11B</t>
+          <t>73.30B</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Constellation Energy Corporation</t>
+          <t>General Dynamics Corporation</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>72.67B</t>
+          <t>72.21B</t>
         </is>
       </c>
     </row>
@@ -2906,143 +2906,143 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>71.21B</t>
+          <t>71.19B</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TransDigm Group Incorporated</t>
+          <t>3M Company</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>70.94B</t>
+          <t>70.66B</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3M Company</t>
+          <t>Capital One Financial Corporation</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>70.67B</t>
+          <t>70.48B</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Capital One Financial Corporation</t>
+          <t>Ecolab Inc.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>70.17B</t>
+          <t>70.45B</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Air Products and Chemicals, Inc.</t>
+          <t>Northrop Grumman Corporation</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>70.10B</t>
+          <t>70.15B</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>TDG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corporation</t>
+          <t>TransDigm Group Incorporated</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>69.96B</t>
+          <t>69.75B</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>FedEx Corporation</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>69.96B</t>
+          <t>69.31B</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>Air Products and Chemicals, Inc.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>69.40B</t>
+          <t>69.14B</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FedEx Corporation</t>
+          <t>The Williams Companies, Inc.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>68.24B</t>
+          <t>67.28B</t>
         </is>
       </c>
     </row>
@@ -3059,160 +3059,160 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>67.30B</t>
+          <t>66.53B</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>The Williams Companies, Inc.</t>
+          <t>Autodesk, Inc.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>66.50B</t>
+          <t>66.46B</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Republic Services, Inc.</t>
+          <t>Carrier Global Corporation</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>66.29B</t>
+          <t>65.98B</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Royal Caribbean Cruises Ltd.</t>
+          <t>Republic Services, Inc.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>66.05B</t>
+          <t>65.80B</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Becton, Dickinson and Company</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>65.89B</t>
+          <t>65.68B</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Carrier Global Corporation</t>
+          <t>Royal Caribbean Cruises Ltd.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>65.33B</t>
+          <t>65.65B</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Autodesk, Inc.</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>65.31B</t>
+          <t>64.95B</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Becton, Dickinson and Company</t>
+          <t>Digital Realty Trust, Inc.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>64.02B</t>
+          <t>63.27B</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Digital Realty Trust, Inc.</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>62.79B</t>
+          <t>62.39B</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>Hilton Worldwide Holdings Inc.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>62.27B</t>
+          <t>62.38B</t>
         </is>
       </c>
     </row>
@@ -3229,109 +3229,109 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>61.88B</t>
+          <t>61.99B</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Hilton Worldwide Holdings Inc.</t>
+          <t>Charter Communications, Inc.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>61.85B</t>
+          <t>61.88B</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Truist Financial Corporation</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>61.68B</t>
+          <t>61.71B</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan Inc.</t>
+          <t>ONEOK, Inc.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>61.31B</t>
+          <t>61.03B</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ONEOK, Inc.</t>
+          <t>Truist Financial Corporation</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>60.95B</t>
+          <t>60.69B</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PACCAR Inc</t>
+          <t>Freeport-McMoRan Inc.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>60.49B</t>
+          <t>60.47B</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Charter Communications, Inc.</t>
+          <t>Copart, Inc.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>60.21B</t>
+          <t>59.82B</t>
         </is>
       </c>
     </row>
@@ -3348,24 +3348,24 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>59.74B</t>
+          <t>59.76B</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Copart, Inc.</t>
+          <t>PACCAR Inc</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>59.28B</t>
+          <t>59.14B</t>
         </is>
       </c>
     </row>
@@ -3382,36 +3382,36 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>58.92B</t>
+          <t>58.76B</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>Schlumberger Limited</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>58.62B</t>
+          <t>58.04B</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Aflac Incorporated</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3423,51 +3423,51 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>BK</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Norfolk Southern Corporation</t>
+          <t>The Bank of New York Mellon Corporation</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>57.94B</t>
+          <t>57.85B</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Aflac Incorporated</t>
+          <t>MetLife, Inc.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>57.90B</t>
+          <t>57.62B</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Schlumberger Limited</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>57.71B</t>
+          <t>57.51B</t>
         </is>
       </c>
     </row>
@@ -3484,24 +3484,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>57.60B</t>
+          <t>56.33B</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MetLife, Inc.</t>
+          <t>Norfolk Southern Corporation</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>56.60B</t>
+          <t>56.18B</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>56.58B</t>
+          <t>56.15B</t>
         </is>
       </c>
     </row>
@@ -3535,41 +3535,41 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>56.37B</t>
+          <t>55.96B</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>The Travelers Companies, Inc.</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>56.22B</t>
+          <t>55.69B</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>The Travelers Companies, Inc.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>56.09B</t>
+          <t>55.37B</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>55.39B</t>
+          <t>55.34B</t>
         </is>
       </c>
     </row>
@@ -3603,41 +3603,41 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>54.82B</t>
+          <t>55.18B</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ameriprise Financial, Inc.</t>
+          <t>Fair Isaac Corporation</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>53.00B</t>
+          <t>53.34B</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Fair Isaac Corporation</t>
+          <t>Ameriprise Financial, Inc.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>52.90B</t>
+          <t>53.15B</t>
         </is>
       </c>
     </row>
@@ -3654,245 +3654,245 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>52.24B</t>
+          <t>51.62B</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>51.88B</t>
+          <t>51.47B</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Cummins Inc.</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>51.82B</t>
+          <t>51.21B</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Ross Stores, Inc.</t>
+          <t>The Allstate Corporation</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>51.68B</t>
+          <t>50.92B</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>The Allstate Corporation</t>
+          <t>Cummins Inc.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>51.65B</t>
+          <t>50.84B</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>51.55B</t>
+          <t>50.81B</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Ross Stores, Inc.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>51.25B</t>
+          <t>50.77B</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>American Electric Power Company, Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>50.65B</t>
+          <t>49.84B</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DHI</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>D.R. Horton, Inc.</t>
+          <t>Quanta Services, Inc.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>50.42B</t>
+          <t>49.61B</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>American Electric Power Company, Inc.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>49.30B</t>
+          <t>49.45B</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Realty Income Corporation</t>
+          <t>Vistra Corp.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>48.97B</t>
+          <t>49.36B</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Axon Enterprise, Inc.</t>
+          <t>D.R. Horton, Inc.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>48.61B</t>
+          <t>48.56B</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation</t>
+          <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>48.55B</t>
+          <t>48.53B</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Lululemon Athletica Inc.</t>
+          <t>Realty Income Corporation</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>48.36B</t>
+          <t>48.41B</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Vistra Corp.</t>
+          <t>Lululemon Athletica Inc.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>48.15B</t>
+          <t>47.41B</t>
         </is>
       </c>
     </row>
@@ -3909,228 +3909,228 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>47.64B</t>
+          <t>47.37B</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Quanta Services, Inc.</t>
+          <t>Newmont Corporation</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>47.22B</t>
+          <t>47.11B</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Newmont Corporation</t>
+          <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>47.03B</t>
+          <t>47.01B</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Howmet Aerospace Inc.</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>46.35B</t>
+          <t>46.48B</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Howmet Aerospace Inc.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>46.23B</t>
+          <t>46.19B</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Dominion Energy, Inc.</t>
+          <t>Keurig Dr Pepper Inc.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>46.21B</t>
+          <t>45.86B</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Cencora, Inc.</t>
+          <t>The Kroger Co.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>45.81B</t>
+          <t>45.80B</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Fastenal Company</t>
+          <t>Fidelity National Information Services, Inc.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>45.70B</t>
+          <t>45.71B</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Fidelity National Information Services, Inc.</t>
+          <t>Fastenal Company</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>45.67B</t>
+          <t>45.28B</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>American International Group, Inc.</t>
+          <t>TE Connectivity plc</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>45.54B</t>
+          <t>45.27B</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper Inc.</t>
+          <t>Occidental Petroleum Corporation</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>45.47B</t>
+          <t>45.22B</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corporation</t>
+          <t>Dominion Energy, Inc.</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>45.09B</t>
+          <t>45.22B</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>TE Connectivity plc</t>
+          <t>American International Group, Inc.</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>44.95B</t>
+          <t>45.20B</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Kimberly-Clark Corporation</t>
+          <t>Cencora, Inc.</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>44.38B</t>
+          <t>44.86B</t>
         </is>
       </c>
     </row>
@@ -4147,75 +4147,75 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>44.13B</t>
+          <t>44.10B</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Constellation Brands, Inc.</t>
+          <t>Kimberly-Clark Corporation</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>44.04B</t>
+          <t>43.65B</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>The Kroger Co.</t>
+          <t>Edwards Lifesciences Corporation</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>43.94B</t>
+          <t>43.63B</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HES</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Hess Corporation</t>
+          <t>AMETEK, Inc.</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>43.87B</t>
+          <t>43.59B</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Lennar Corporation</t>
+          <t>Constellation Brands, Inc.</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>43.85B</t>
+          <t>43.47B</t>
         </is>
       </c>
     </row>
@@ -4232,398 +4232,398 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>43.79B</t>
+          <t>43.35B</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>HES</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>L3Harris Technologies, Inc.</t>
+          <t>Hess Corporation</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>43.75B</t>
+          <t>43.32B</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Crown Castle Inc.</t>
+          <t>Prudential Financial, Inc.</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>43.70B</t>
+          <t>42.94B</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>AMETEK, Inc.</t>
+          <t>Crown Castle Inc.</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>43.62B</t>
+          <t>42.93B</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Kenvue Inc.</t>
+          <t>Public Service Enterprise Group Incorporated</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>43.60B</t>
+          <t>42.82B</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Electronic Arts Inc.</t>
+          <t>Kenvue Inc.</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>43.35B</t>
+          <t>42.79B</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corporation</t>
+          <t>Electronic Arts Inc.</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>43.29B</t>
+          <t>42.64B</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Prudential Financial, Inc.</t>
+          <t>PG&amp;E Corporation</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>43.16B</t>
+          <t>42.58B</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group Incorporated</t>
+          <t>L3Harris Technologies, Inc.</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>43.04B</t>
+          <t>42.55B</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PCG</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PG&amp;E Corporation</t>
+          <t>Lennar Corporation</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>42.49B</t>
+          <t>42.17B</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Garmin Ltd.</t>
+          <t>CBRE Group, Inc.</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>42.09B</t>
+          <t>42.02B</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Baker Hughes Company</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>41.97B</t>
+          <t>41.89B</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Valero Energy Corporation</t>
+          <t>Corning Incorporated</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>41.89B</t>
+          <t>41.62B</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Corning Incorporated</t>
+          <t>Garmin Ltd.</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>41.41B</t>
+          <t>41.47B</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Ingersoll Rand Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>41.04B</t>
+          <t>41.29B</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CBRE Group, Inc.</t>
+          <t>Valero Energy Corporation</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>40.87B</t>
+          <t>41.05B</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Corteva, Inc.</t>
+          <t>Ingersoll Rand Inc.</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>40.84B</t>
+          <t>40.87B</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Baker Hughes Company</t>
+          <t>Corteva, Inc.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>40.78B</t>
+          <t>40.76B</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Targa Resources Corp.</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>40.48B</t>
+          <t>40.47B</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Agilent Technologies, Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>40.48B</t>
+          <t>40.29B</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Targa Resources Corp.</t>
+          <t>Agilent Technologies, Inc.</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>40.42B</t>
+          <t>40.19B</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Delta Air Lines, Inc.</t>
+          <t>Cognizant Technology Solutions Corporation</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>40.24B</t>
+          <t>39.85B</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Otis Worldwide Corporation</t>
+          <t>Gartner, Inc.</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>39.97B</t>
+          <t>39.66B</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Las Vegas Sands Corp.</t>
+          <t>Delta Air Lines, Inc.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>39.79B</t>
+          <t>39.51B</t>
         </is>
       </c>
     </row>
@@ -4640,58 +4640,58 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>39.71B</t>
+          <t>39.33B</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Sysco Corporation</t>
+          <t>Otis Worldwide Corporation</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>39.70B</t>
+          <t>39.25B</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions Corporation</t>
+          <t>Sysco Corporation</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>39.70B</t>
+          <t>39.18B</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Gartner, Inc.</t>
+          <t>Las Vegas Sands Corp.</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>39.54B</t>
+          <t>39.01B</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>38.57B</t>
+          <t>38.69B</t>
         </is>
       </c>
     </row>
@@ -4725,41 +4725,41 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>38.20B</t>
+          <t>38.15B</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>GE HealthCare Technologies Inc.</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>37.88B</t>
+          <t>37.29B</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>GE HealthCare Technologies Inc.</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>37.63B</t>
+          <t>37.22B</t>
         </is>
       </c>
     </row>
@@ -4776,24 +4776,24 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>37.50B</t>
+          <t>37.01B</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>IQVIA Holdings Inc.</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>36.88B</t>
+          <t>36.73B</t>
         </is>
       </c>
     </row>
@@ -4810,24 +4810,24 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>36.72B</t>
+          <t>36.68B</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>IQVIA Holdings Inc.</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>36.49B</t>
+          <t>36.37B</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>36.42B</t>
+          <t>35.80B</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>35.99B</t>
+          <t>35.59B</t>
         </is>
       </c>
     </row>
@@ -4878,109 +4878,109 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>35.54B</t>
+          <t>35.38B</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Extra Space Storage Inc.</t>
+          <t>Arch Capital Group Ltd.</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>35.38B</t>
+          <t>35.19B</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Arch Capital Group Ltd.</t>
+          <t>Extra Space Storage Inc.</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>34.98B</t>
+          <t>35.06B</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Martin Marietta Materials, Inc.</t>
+          <t>Rockwell Automation, Inc.</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>34.44B</t>
+          <t>34.20B</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>DuPont de Nemours, Inc.</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>34.42B</t>
+          <t>34.09B</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>M&amp;T Bank Corporation</t>
+          <t>Martin Marietta Materials, Inc.</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>34.34B</t>
+          <t>34.03B</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DuPont de Nemours, Inc.</t>
+          <t>Carnival Corporation &amp; plc</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>34.31B</t>
+          <t>34.01B</t>
         </is>
       </c>
     </row>
@@ -4997,245 +4997,245 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>33.67B</t>
+          <t>33.71B</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Carnival Corporation &amp; plc</t>
+          <t>Take-Two Interactive Software, Inc.</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>33.55B</t>
+          <t>33.31B</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>M&amp;T Bank Corporation</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>33.25B</t>
+          <t>33.18B</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Rockwell Automation, Inc.</t>
+          <t>Iron Mountain Incorporated</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>33.16B</t>
+          <t>33.14B</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>VICI Properties Inc.</t>
+          <t>Microchip Technology Incorporated</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>33.14B</t>
+          <t>33.03B</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Nucor Corporation</t>
+          <t>Equifax Inc.</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>33.01B</t>
+          <t>32.88B</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Iron Mountain Incorporated</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>32.87B</t>
+          <t>32.85B</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Raymond James Financial, Inc.</t>
+          <t>VICI Properties Inc.</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>32.83B</t>
+          <t>32.77B</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Consolidated Edison, Inc.</t>
+          <t>Raymond James Financial, Inc.</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>32.80B</t>
+          <t>32.72B</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>AVB</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>The Hartford Financial Services Group, Inc.</t>
+          <t>AvalonBay Communities, Inc.</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>32.75B</t>
+          <t>32.38B</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software, Inc.</t>
+          <t>The Hartford Financial Services Group, Inc.</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>32.55B</t>
+          <t>32.15B</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Equifax Inc.</t>
+          <t>Consolidated Edison, Inc.</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>32.30B</t>
+          <t>32.08B</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>CoStar Group, Inc.</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>32.05B</t>
+          <t>32.08B</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>AVB</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>AvalonBay Communities, Inc.</t>
+          <t>Entergy Corporation</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>31.97B</t>
+          <t>31.79B</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Entergy Corporation</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>31.80B</t>
+          <t>31.60B</t>
         </is>
       </c>
     </row>
@@ -5252,143 +5252,143 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>31.75B</t>
+          <t>31.56B</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>LYV</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CoStar Group, Inc.</t>
+          <t>Live Nation Entertainment, Inc.</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>31.33B</t>
+          <t>31.32B</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Willis Towers Watson Public Limited Company</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>31.24B</t>
+          <t>31.06B</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Deckers Outdoor Corporation</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>31.11B</t>
+          <t>30.94B</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DexCom, Inc.</t>
+          <t>Nucor Corporation</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>31.02B</t>
+          <t>30.86B</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Willis Towers Watson Public Limited Company</t>
+          <t>DexCom, Inc.</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>30.99B</t>
+          <t>30.83B</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>LYV</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Live Nation Entertainment, Inc.</t>
+          <t>Warner Bros. Discovery, Inc.</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>30.98B</t>
+          <t>30.64B</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>WEC Energy Group, Inc.</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>30.73B</t>
+          <t>30.61B</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Deckers Outdoor Corporation</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>30.71B</t>
+          <t>30.53B</t>
         </is>
       </c>
     </row>
@@ -5405,92 +5405,92 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>30.42B</t>
+          <t>30.48B</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>WEC Energy Group, Inc.</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>30.29B</t>
+          <t>30.33B</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>ANSS</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Corporation</t>
+          <t>ANSYS, Inc.</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>29.78B</t>
+          <t>29.87B</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ANSS</t>
+          <t>BRO</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ANSYS, Inc.</t>
+          <t>Brown &amp; Brown, Inc.</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>29.71B</t>
+          <t>29.64B</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>The Estée Lauder Companies Inc.</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>29.64B</t>
+          <t>29.53B</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Dow Inc.</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>29.63B</t>
+          <t>29.49B</t>
         </is>
       </c>
     </row>
@@ -5514,80 +5514,80 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown, Inc.</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>29.43B</t>
+          <t>29.41B</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>GoDaddy Inc.</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>29.32B</t>
+          <t>29.33B</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Keysight Technologies, Inc.</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>29.15B</t>
+          <t>29.28B</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Cardinal Health, Inc.</t>
+          <t>The Estée Lauder Companies Inc.</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>29.14B</t>
+          <t>29.08B</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PPG Industries, Inc.</t>
+          <t>Keysight Technologies, Inc.</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -5599,80 +5599,80 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>Dow Inc.</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>29.04B</t>
+          <t>29.00B</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>EQR</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>GoDaddy Inc.</t>
+          <t>Equity Residential</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>28.76B</t>
+          <t>28.85B</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>PPG Industries, Inc.</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>28.63B</t>
+          <t>28.74B</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>EQR</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Equity Residential</t>
+          <t>ON Semiconductor Corporation</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>28.50B</t>
+          <t>28.58B</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Company</t>
+          <t>Cardinal Health, Inc.</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -5684,17 +5684,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ON Semiconductor Corporation</t>
+          <t>Hewlett Packard Enterprise Company</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>28.25B</t>
+          <t>28.31B</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>27.68B</t>
+          <t>27.69B</t>
         </is>
       </c>
     </row>
@@ -5769,34 +5769,34 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>T. Rowe Price Group, Inc.</t>
+          <t>Texas Pacific Land Corporation</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>27.33B</t>
+          <t>27.50B</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>FTV</t>
+          <t>EQT</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Fortive Corporation</t>
+          <t>EQT Corporation</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>27.17B</t>
+          <t>27.36B</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>27.14B</t>
+          <t>26.95B</t>
         </is>
       </c>
     </row>
@@ -5830,449 +5830,449 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>26.81B</t>
+          <t>26.95B</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery, Inc.</t>
+          <t>Tyler Technologies, Inc.</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>26.71B</t>
+          <t>26.89B</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Tyler Technologies, Inc.</t>
+          <t>T. Rowe Price Group, Inc.</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>26.43B</t>
+          <t>26.87B</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Veralto Corporation</t>
+          <t>Synchrony Financial</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>26.31B</t>
+          <t>26.68B</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>FTV</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co., Inc.</t>
+          <t>Fortive Corporation</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>26.23B</t>
+          <t>26.66B</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Synchrony Financial</t>
+          <t>Veralto Corporation</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>26.04B</t>
+          <t>26.16B</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Ventas, Inc.</t>
+          <t>Church &amp; Dwight Co., Inc.</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>25.86B</t>
+          <t>25.83B</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PulteGroup, Inc.</t>
+          <t>American Water Works Company, Inc.</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>25.71B</t>
+          <t>25.44B</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>EQT Corporation</t>
+          <t>Archer-Daniels-Midland Company</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>25.69B</t>
+          <t>25.40B</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Halliburton Company</t>
+          <t>Ventas, Inc.</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>25.54B</t>
+          <t>25.39B</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>American Water Works Company, Inc.</t>
+          <t>Halliburton Company</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>25.53B</t>
+          <t>25.38B</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DTE Energy Company</t>
+          <t>Corpay, Inc.</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>25.26B</t>
+          <t>25.20B</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>LyondellBasell Industries N.V.</t>
+          <t>NetApp, Inc.</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>25.21B</t>
+          <t>25.11B</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Huntington Bancshares Incorporated</t>
+          <t>DTE Energy Company</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>25.05B</t>
+          <t>25.01B</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company</t>
+          <t>Huntington Bancshares Incorporated</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>24.92B</t>
+          <t>24.94B</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Corpay, Inc.</t>
+          <t>PulteGroup, Inc.</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>24.90B</t>
+          <t>24.75B</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>NetApp, Inc.</t>
+          <t>LyondellBasell Industries N.V.</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>24.64B</t>
+          <t>24.74B</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Ameren Corporation</t>
+          <t>Hubbell Incorporated</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>24.35B</t>
+          <t>24.44B</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PPL Corporation</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>24.29B</t>
+          <t>24.18B</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Expedia Group, Inc.</t>
+          <t>West Pharmaceutical Services, Inc.</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>24.18B</t>
+          <t>24.02B</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Hubbell Incorporated</t>
+          <t>Ameren Corporation</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>24.08B</t>
+          <t>23.97B</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>PPL Corporation</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>23.86B</t>
+          <t>23.83B</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Cincinnati Financial Corporation</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>23.83B</t>
+          <t>23.78B</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>23.79B</t>
+          <t>23.73B</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>Expedia Group, Inc.</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>23.79B</t>
+          <t>23.69B</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>23.74B</t>
+          <t>23.62B</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Cincinnati Financial Corporation</t>
+          <t>FirstEnergy Corp.</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>23.42B</t>
+          <t>23.24B</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>23.37B</t>
+          <t>23.23B</t>
         </is>
       </c>
     </row>
@@ -6306,160 +6306,160 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>23.36B</t>
+          <t>23.05B</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>FirstEnergy Corp.</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>23.34B</t>
+          <t>22.81B</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Regions Financial Corporation</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>23.18B</t>
+          <t>22.77B</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services, Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>23.12B</t>
+          <t>22.74B</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Regions Financial Corporation</t>
+          <t>Biogen Inc.</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>23.02B</t>
+          <t>22.63B</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Devon Energy Corporation</t>
+          <t>International Flavors &amp; Fragrances Inc.</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>22.81B</t>
+          <t>22.53B</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Biogen Inc.</t>
+          <t>Devon Energy Corporation</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>22.78B</t>
+          <t>22.42B</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances Inc.</t>
+          <t>Teledyne Technologies Incorporated</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>22.64B</t>
+          <t>22.32B</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Weyerhaeuser Company</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>22.47B</t>
+          <t>22.21B</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>Weyerhaeuser Company</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>22.21B</t>
+          <t>22.09B</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>22.18B</t>
+          <t>21.91B</t>
         </is>
       </c>
     </row>
@@ -6493,138 +6493,138 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>21.99B</t>
+          <t>21.85B</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Teledyne Technologies Incorporated</t>
+          <t>Atmos Energy Corporation</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>21.95B</t>
+          <t>21.79B</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Atmos Energy Corporation</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>21.93B</t>
+          <t>21.78B</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>First Solar, Inc.</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>21.72B</t>
+          <t>21.62B</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Zimmer Biomet Holdings, Inc.</t>
+          <t>Erie Indemnity Company</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>21.58B</t>
+          <t>21.48B</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation</t>
+          <t>STERIS plc</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>21.44B</t>
+          <t>21.36B</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Leidos Holdings, Inc.</t>
+          <t>Packaging Corporation of America</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>21.37B</t>
+          <t>21.32B</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>BF.B</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Brown-Forman Corporation</t>
+          <t>Zimmer Biomet Holdings, Inc.</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>21.35B</t>
+          <t>21.27B</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>BF.B</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Cboe Global Markets, Inc.</t>
+          <t>Brown-Forman Corporation</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -6636,102 +6636,102 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Packaging Corporation of America</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>21.24B</t>
+          <t>21.06B</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Zebra Technologies Corporation</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>21.18B</t>
+          <t>21.03B</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>STERIS plc</t>
+          <t>First Solar, Inc.</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>21.15B</t>
+          <t>21.02B</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Erie Indemnity Company</t>
+          <t>Cboe Global Markets, Inc.</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>21.00B</t>
+          <t>20.92B</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>Northern Trust Corporation</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>20.75B</t>
+          <t>20.89B</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Zebra Technologies Corporation</t>
+          <t>CenterPoint Energy, Inc.</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>20.72B</t>
+          <t>20.80B</t>
         </is>
       </c>
     </row>
@@ -6748,75 +6748,75 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>20.64B</t>
+          <t>20.65B</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Leidos Holdings, Inc.</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>20.60B</t>
+          <t>20.41B</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Steel Dynamics, Inc.</t>
+          <t>Invitation Homes Inc.</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>20.60B</t>
+          <t>20.39B</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Invitation Homes Inc.</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>20.47B</t>
+          <t>20.38B</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>CenterPoint Energy, Inc.</t>
+          <t>Essex Property Trust, Inc.</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>20.45B</t>
+          <t>20.13B</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>20.45B</t>
+          <t>20.07B</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>20.22B</t>
+          <t>20.03B</t>
         </is>
       </c>
     </row>
@@ -6867,228 +6867,228 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>20.06B</t>
+          <t>19.93B</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Essex Property Trust, Inc.</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>19.82B</t>
+          <t>19.70B</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Darden Restaurants, Inc.</t>
+          <t>Ulta Beauty, Inc.</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>19.78B</t>
+          <t>19.66B</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>BLDR</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>The Cooper Companies, Inc.</t>
+          <t>Builders FirstSource, Inc.</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>19.77B</t>
+          <t>19.64B</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Builders FirstSource, Inc.</t>
+          <t>Labcorp Holdings Inc.</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>19.65B</t>
+          <t>19.39B</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Labcorp Holdings Inc.</t>
+          <t>Darden Restaurants, Inc.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>19.62B</t>
+          <t>19.39B</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Insulet Corporation</t>
+          <t>Steel Dynamics, Inc.</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>19.28B</t>
+          <t>19.32B</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>VeriSign, Inc.</t>
+          <t>The Cooper Companies, Inc.</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>19.27B</t>
+          <t>19.30B</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Ulta Beauty, Inc.</t>
+          <t>NRG Energy, Inc.</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>19.10B</t>
+          <t>19.27B</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>VeriSign, Inc.</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>19.06B</t>
+          <t>19.13B</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>International Paper Company</t>
+          <t>Insulet Corporation</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>19.02B</t>
+          <t>19.06B</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities, Inc.</t>
+          <t>International Paper Company</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>19.02B</t>
+          <t>19.06B</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>NRG Energy, Inc.</t>
+          <t>Mid-America Apartment Communities, Inc.</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>18.99B</t>
+          <t>19.00B</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>CTRA</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Snap-on Incorporated</t>
+          <t>Coterra Energy Inc.</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>18.62B</t>
+          <t>18.90B</t>
         </is>
       </c>
     </row>
@@ -7105,364 +7105,364 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>18.54B</t>
+          <t>18.90B</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Principal Financial Group, Inc.</t>
+          <t>Snap-on Incorporated</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>18.47B</t>
+          <t>18.67B</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Hormel Foods Corporation</t>
+          <t>FactSet Research Systems Inc.</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>18.42B</t>
+          <t>18.56B</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Services, Inc.</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>18.38B</t>
+          <t>18.50B</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>FactSet Research Systems Inc.</t>
+          <t>Trimble Inc.</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>18.38B</t>
+          <t>18.28B</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Loews Corporation</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>18.38B</t>
+          <t>18.28B</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Loews Corporation</t>
+          <t>J.B. Hunt Transport Services, Inc.</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>18.28B</t>
+          <t>18.27B</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CTRA</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Coterra Energy Inc.</t>
+          <t>Hormel Foods Corporation</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>18.28B</t>
+          <t>18.14B</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Alexandria Real Estate Equities, Inc.</t>
+          <t>Principal Financial Group, Inc.</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>18.26B</t>
+          <t>18.14B</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>KeyCorp</t>
+          <t>Alexandria Real Estate Equities, Inc.</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>18.25B</t>
+          <t>17.94B</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Dollar General Corporation</t>
+          <t>KeyCorp</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>18.12B</t>
+          <t>17.90B</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>Pentair plc</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>18.10B</t>
+          <t>17.89B</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Omnicom Group Inc.</t>
+          <t>Align Technology, Inc.</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>18.04B</t>
+          <t>17.60B</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Pentair plc</t>
+          <t>Omnicom Group Inc.</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>17.82B</t>
+          <t>17.59B</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Align Technology, Inc.</t>
+          <t>Quest Diagnostics Incorporated</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>17.70B</t>
+          <t>17.42B</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Quest Diagnostics Incorporated</t>
+          <t>Ball Corporation</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>17.69B</t>
+          <t>17.31B</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>HOLX</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Hologic, Inc.</t>
+          <t>Dollar General Corporation</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>17.44B</t>
+          <t>17.25B</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Genuine Parts Company</t>
+          <t>Masco Corporation</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>17.44B</t>
+          <t>17.09B</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>IDEX Corporation</t>
+          <t>NiSource Inc.</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>17.26B</t>
+          <t>17.05B</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>HOLX</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Masco Corporation</t>
+          <t>Hologic, Inc.</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>17.12B</t>
+          <t>17.04B</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>IDEX Corporation</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>17.11B</t>
+          <t>17.04B</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>NiSource Inc.</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>17.09B</t>
+          <t>17.01B</t>
         </is>
       </c>
     </row>
@@ -7479,138 +7479,138 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>17.06B</t>
+          <t>17.00B</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Ball Corporation</t>
+          <t>Genuine Parts Company</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>17.03B</t>
+          <t>16.93B</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington, Inc.</t>
+          <t>Jacobs Solutions Inc.</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>16.95B</t>
+          <t>16.86B</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Jacobs Solutions Inc.</t>
+          <t>Expeditors International of Washington, Inc.</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>16.87B</t>
+          <t>16.76B</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>UDR, Inc.</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>16.70B</t>
+          <t>16.71B</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>UDR, Inc.</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>16.59B</t>
+          <t>16.53B</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>News Corporation</t>
+          <t>Moderna, Inc.</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>16.51B</t>
+          <t>16.48B</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Avery Dennison Corporation</t>
+          <t>News Corporation</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>16.19B</t>
+          <t>16.47B</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Baxter International Inc.</t>
+          <t>Domino's Pizza, Inc.</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -7622,51 +7622,51 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Moderna, Inc.</t>
+          <t>Avery Dennison Corporation</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>15.97B</t>
+          <t>15.88B</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Domino's Pizza, Inc.</t>
+          <t>Baxter International Inc.</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>15.68B</t>
+          <t>15.75B</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Dollar Tree, Inc.</t>
+          <t>CF Industries Holdings, Inc.</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>15.65B</t>
+          <t>15.68B</t>
         </is>
       </c>
     </row>
@@ -7700,36 +7700,36 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>15.58B</t>
+          <t>15.52B</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>CF Industries Holdings, Inc.</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>15.46B</t>
+          <t>15.33B</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Healthpeak Properties, Inc.</t>
+          <t>Viatris Inc.</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -7741,85 +7741,85 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Textron Inc.</t>
+          <t>Dollar Tree, Inc.</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>15.22B</t>
+          <t>15.23B</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Jabil Inc.</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>14.98B</t>
+          <t>15.08B</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Jabil Inc.</t>
+          <t>Textron Inc.</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>14.98B</t>
+          <t>15.04B</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Viatris Inc.</t>
+          <t>Akamai Technologies, Inc.</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>14.93B</t>
+          <t>15.02B</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Akamai Technologies, Inc.</t>
+          <t>Healthpeak Properties, Inc.</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>14.84B</t>
+          <t>14.93B</t>
         </is>
       </c>
     </row>
@@ -7836,41 +7836,41 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>14.59B</t>
+          <t>14.39B</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Skyworks Solutions, Inc.</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>14.46B</t>
+          <t>14.34B</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Revvity, Inc.</t>
+          <t>Tapestry, Inc.</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>14.34B</t>
+          <t>14.33B</t>
         </is>
       </c>
     </row>
@@ -7887,75 +7887,75 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>14.34B</t>
+          <t>14.29B</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>14.32B</t>
+          <t>14.18B</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Tapestry, Inc.</t>
+          <t>Revvity, Inc.</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>14.31B</t>
+          <t>14.12B</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>14.27B</t>
+          <t>14.10B</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>14.19B</t>
+          <t>14.06B</t>
         </is>
       </c>
     </row>
@@ -7972,75 +7972,75 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>14.12B</t>
+          <t>14.04B</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Skyworks Solutions, Inc.</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>14.02B</t>
+          <t>13.76B</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Incyte Corporation</t>
+          <t>Regency Centers Corporation</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>13.96B</t>
+          <t>13.72B</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>Incyte Corporation</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>13.73B</t>
+          <t>13.65B</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Regency Centers Corporation</t>
+          <t>C.H. Robinson Worldwide, Inc.</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>13.54B</t>
+          <t>13.48B</t>
         </is>
       </c>
     </row>
@@ -8057,24 +8057,24 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>13.34B</t>
+          <t>13.44B</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>PAYC</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Host Hotels &amp; Resorts, Inc.</t>
+          <t>Paycom Software, Inc.</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>13.33B</t>
+          <t>13.41B</t>
         </is>
       </c>
     </row>
@@ -8091,177 +8091,177 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>13.29B</t>
+          <t>13.40B</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Jack Henry &amp; Associates, Inc.</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>13.20B</t>
+          <t>13.17B</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>PAYC</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Paycom Software, Inc.</t>
+          <t>Host Hotels &amp; Resorts, Inc.</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>13.17B</t>
+          <t>13.16B</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>The Campbell's Company</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>12.98B</t>
+          <t>13.10B</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker, Inc.</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>12.93B</t>
+          <t>13.10B</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates, Inc.</t>
+          <t>The Campbell's Company</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>12.93B</t>
+          <t>12.79B</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>C.H. Robinson Worldwide, Inc.</t>
+          <t>Stanley Black &amp; Decker, Inc.</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>12.91B</t>
+          <t>12.75B</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Molson Coors Beverage Company</t>
+          <t>DaVita Inc.</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>12.69B</t>
+          <t>12.62B</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>TAP</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Universal Health Services, Inc.</t>
+          <t>Molson Coors Beverage Company</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>12.65B</t>
+          <t>12.55B</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>DVA</t>
+          <t>JNPR</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>DaVita Inc.</t>
+          <t>Juniper Networks, Inc.</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>12.61B</t>
+          <t>12.35B</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>JNPR</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Juniper Networks, Inc.</t>
+          <t>Universal Health Services, Inc.</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>12.33B</t>
+          <t>12.30B</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>12.29B</t>
+          <t>12.23B</t>
         </is>
       </c>
     </row>
@@ -8295,126 +8295,126 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>12.25B</t>
+          <t>12.18B</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>The J. M. Smucker Company</t>
+          <t>Albemarle Corporation</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>12.24B</t>
+          <t>12.14B</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Albemarle Corporation</t>
+          <t>Allegion plc</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>12.22B</t>
+          <t>12.10B</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Allegion plc</t>
+          <t>Solventum Corporation</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>12.22B</t>
+          <t>12.09B</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Solventum Corporation</t>
+          <t>The J. M. Smucker Company</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>12.04B</t>
+          <t>12.08B</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Bunge Global SA</t>
+          <t>Norwegian Cruise Line Holdings Ltd.</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>11.83B</t>
+          <t>11.79B</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Franklin Resources, Inc.</t>
+          <t>Bunge Global SA</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>11.70B</t>
+          <t>11.67B</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings Ltd.</t>
+          <t>Franklin Resources, Inc.</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>11.61B</t>
+          <t>11.57B</t>
         </is>
       </c>
     </row>
@@ -8431,53 +8431,53 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>11.51B</t>
+          <t>11.56B</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>IPG</t>
+          <t>CTLT</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>The Interpublic Group of Companies, Inc.</t>
+          <t>Catalent, Inc.</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>11.32B</t>
+          <t>11.44B</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CTLT</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Catalent, Inc.</t>
+          <t>Assurant, Inc.</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>11.30B</t>
+          <t>11.16B</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>IPG</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Assurant, Inc.</t>
+          <t>The Interpublic Group of Companies, Inc.</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>10.87B</t>
+          <t>10.96B</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>10.81B</t>
+          <t>10.59B</t>
         </is>
       </c>
     </row>
@@ -8533,19 +8533,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>10.58B</t>
+          <t>10.53B</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>GNRC</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Wynn Resorts, Limited</t>
+          <t>Generac Holdings Inc.</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -8557,119 +8557,119 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Pinnacle West Capital Corporation</t>
+          <t>Wynn Resorts, Limited</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>10.26B</t>
+          <t>10.17B</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>GNRC</t>
+          <t>PNW</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Generac Holdings Inc.</t>
+          <t>Pinnacle West Capital Corporation</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>10.19B</t>
+          <t>10.09B</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>LKQ</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Charles River Laboratories International, Inc.</t>
+          <t>LKQ Corporation</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>10.08B</t>
+          <t>9.97B</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>ENPH</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Enphase Energy, Inc.</t>
+          <t>Charles River Laboratories International, Inc.</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>10.06B</t>
+          <t>9.93B</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>LKQ</t>
+          <t>ENPH</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>LKQ Corporation</t>
+          <t>Enphase Energy, Inc.</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>10.06B</t>
+          <t>9.86B</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>The AES Corporation</t>
+          <t>Federal Realty Investment Trust</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>9.70B</t>
+          <t>9.71B</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust</t>
+          <t>The AES Corporation</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>9.65B</t>
+          <t>9.61B</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>9.32B</t>
+          <t>9.60B</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>9.12B</t>
+          <t>8.94B</t>
         </is>
       </c>
     </row>
@@ -8720,104 +8720,104 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>9.05B</t>
+          <t>8.91B</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>WBA</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Walgreens Boots Alliance, Inc.</t>
+          <t>Globe Life Inc.</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>9.01B</t>
+          <t>8.77B</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>TFX</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Globe Life Inc.</t>
+          <t>Teleflex Incorporated</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>8.70B</t>
+          <t>8.51B</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>TFX</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Teleflex Incorporated</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>8.66B</t>
+          <t>8.49B</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Match Group, Inc.</t>
+          <t>The Mosaic Company</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>8.30B</t>
+          <t>8.47B</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>WBA</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Invesco Ltd.</t>
+          <t>Walgreens Boots Alliance, Inc.</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>8.29B</t>
+          <t>8.41B</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>MHK</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Mohawk Industries, Inc.</t>
+          <t>Invesco Ltd.</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -8829,68 +8829,68 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MHK</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>Mohawk Industries, Inc.</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>8.24B</t>
+          <t>8.23B</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>The Mosaic Company</t>
+          <t>Caesars Entertainment, Inc.</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>8.20B</t>
+          <t>8.03B</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>PARA</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Caesars Entertainment, Inc.</t>
+          <t>Paramount Global</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>7.84B</t>
+          <t>7.76B</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Celanese Corporation</t>
+          <t>Match Group, Inc.</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>7.61B</t>
+          <t>7.68B</t>
         </is>
       </c>
     </row>
@@ -8907,36 +8907,36 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>7.57B</t>
+          <t>7.67B</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Huntington Ingalls Industries, Inc.</t>
+          <t>Celanese Corporation</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>7.47B</t>
+          <t>7.53B</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>PARA</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Paramount Global</t>
+          <t>Huntington Ingalls Industries, Inc.</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>7.15B</t>
+          <t>6.80B</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>6.48B</t>
+          <t>6.58B</t>
         </is>
       </c>
     </row>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>5.84B</t>
+          <t>5.74B</t>
         </is>
       </c>
     </row>
